--- a/GURU 99 Banking Website/SRS_v4 GURU99.xlsx
+++ b/GURU 99 Banking Website/SRS_v4 GURU99.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Games\3mk\Manual Testing\GURU 99 Banking Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DD3988-6949-4F64-825A-B6D7934C141B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D45C69-D7B2-43D2-AFA6-B2A3060C7037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="830" firstSheet="4" activeTab="5" xr2:uid="{46F18F15-F5BE-4E77-8066-124D7813421F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="830" firstSheet="4" activeTab="13" xr2:uid="{46F18F15-F5BE-4E77-8066-124D7813421F}"/>
   </bookViews>
   <sheets>
     <sheet name="NEW ACCOUNT" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="627">
   <si>
     <t>Title</t>
   </si>
@@ -1982,6 +1982,33 @@
   </si>
   <si>
     <t xml:space="preserve">System displayed confirmation message </t>
+  </si>
+  <si>
+    <t>Error message "Old Password is required"</t>
+  </si>
+  <si>
+    <t>Error message "Incorrect Old Password"</t>
+  </si>
+  <si>
+    <t>Error message "New Password is required"</t>
+  </si>
+  <si>
+    <t>Password changed successfully</t>
+  </si>
+  <si>
+    <t>Error message "Password must contain at least one numeric value"</t>
+  </si>
+  <si>
+    <t>System Accepted the new password data</t>
+  </si>
+  <si>
+    <t>Error message "Password must contain at least one special character"</t>
+  </si>
+  <si>
+    <t>Error message "Confirm Password is required"</t>
+  </si>
+  <si>
+    <t>Error message "Passwords do not match"</t>
   </si>
 </sst>
 </file>
@@ -2250,7 +2277,28 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="20">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3137,7 +3185,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3684,10 +3732,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4229,13 +4277,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4251,10 +4299,11 @@
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="3" max="3" width="18.21875" customWidth="1"/>
-    <col min="4" max="4" width="22.5546875" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" customWidth="1"/>
     <col min="5" max="5" width="27.21875" customWidth="1"/>
-    <col min="6" max="6" width="20.5546875" customWidth="1"/>
+    <col min="6" max="6" width="24.77734375" customWidth="1"/>
     <col min="7" max="7" width="22.77734375" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.8" thickBot="1">
@@ -4286,7 +4335,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="53.4" thickBot="1">
+    <row r="2" spans="1:9" ht="97.2" thickBot="1">
       <c r="A2" s="4" t="s">
         <v>469</v>
       </c>
@@ -4308,14 +4357,14 @@
       <c r="G2" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="H2" s="23" t="s">
-        <v>545</v>
+      <c r="H2" s="26" t="s">
+        <v>618</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="106.2" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="96" customHeight="1" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>469</v>
       </c>
@@ -4337,14 +4386,14 @@
       <c r="G3" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="H3" s="23" t="s">
-        <v>545</v>
+      <c r="H3" s="26" t="s">
+        <v>619</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="53.4" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="159" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>469</v>
       </c>
@@ -4366,14 +4415,14 @@
       <c r="G4" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="H4" s="23" t="s">
-        <v>545</v>
+      <c r="H4" s="26" t="s">
+        <v>620</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="93" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="82.8" customHeight="1" thickBot="1">
       <c r="A5" s="4" t="s">
         <v>469</v>
       </c>
@@ -4395,14 +4444,14 @@
       <c r="G5" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="H5" s="23" t="s">
-        <v>545</v>
+      <c r="H5" s="26" t="s">
+        <v>621</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="93" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="105.6" customHeight="1" thickBot="1">
       <c r="A6" s="4" t="s">
         <v>469</v>
       </c>
@@ -4424,14 +4473,14 @@
       <c r="G6" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>545</v>
+      <c r="H6" s="26" t="s">
+        <v>622</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="93" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="66.599999999999994" thickBot="1">
       <c r="A7" s="4" t="s">
         <v>469</v>
       </c>
@@ -4453,14 +4502,14 @@
       <c r="G7" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>545</v>
+      <c r="H7" s="26" t="s">
+        <v>623</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="93" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="69.599999999999994" thickBot="1">
       <c r="A8" s="4" t="s">
         <v>469</v>
       </c>
@@ -4482,14 +4531,14 @@
       <c r="G8" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>545</v>
+      <c r="H8" s="26" t="s">
+        <v>624</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="93" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="66.599999999999994" thickBot="1">
       <c r="A9" s="4" t="s">
         <v>469</v>
       </c>
@@ -4511,14 +4560,14 @@
       <c r="G9" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="H9" s="23" t="s">
-        <v>545</v>
+      <c r="H9" s="26" t="s">
+        <v>624</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="93" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="66.599999999999994" thickBot="1">
       <c r="A10" s="4" t="s">
         <v>469</v>
       </c>
@@ -4540,14 +4589,14 @@
       <c r="G10" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="H10" s="23" t="s">
-        <v>545</v>
+      <c r="H10" s="26" t="s">
+        <v>623</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="53.4" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="58.2" thickBot="1">
       <c r="A11" s="4" t="s">
         <v>469</v>
       </c>
@@ -4569,14 +4618,14 @@
       <c r="G11" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="H11" s="23" t="s">
-        <v>545</v>
+      <c r="H11" s="26" t="s">
+        <v>625</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="93" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="66.599999999999994" thickBot="1">
       <c r="A12" s="4" t="s">
         <v>469</v>
       </c>
@@ -4598,14 +4647,14 @@
       <c r="G12" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="H12" s="23" t="s">
-        <v>545</v>
+      <c r="H12" s="26" t="s">
+        <v>626</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="93" thickBot="1">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="66.599999999999994" thickBot="1">
       <c r="A13" s="4" t="s">
         <v>469</v>
       </c>
@@ -4627,14 +4676,14 @@
       <c r="G13" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="H13" s="23" t="s">
-        <v>545</v>
+      <c r="H13" s="26" t="s">
+        <v>623</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="93" thickBot="1">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="66.599999999999994" thickBot="1">
       <c r="A14" s="4" t="s">
         <v>469</v>
       </c>
@@ -4656,11 +4705,11 @@
       <c r="G14" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="H14" s="23" t="s">
-        <v>545</v>
+      <c r="H14" s="26" t="s">
+        <v>621</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1">
@@ -4700,6 +4749,14 @@
       <c r="G18" s="3"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="E7" r:id="rId1" xr:uid="{E6E33DFC-EBB6-4751-B322-1208C0A3CA03}"/>
     <hyperlink ref="E10" r:id="rId2" xr:uid="{AB8B7201-6DFC-4C4D-BFE8-FFB27E9FB91D}"/>
@@ -5130,10 +5187,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6410,10 +6467,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6646,10 +6703,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7258,7 +7315,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8114,10 +8171,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9560,10 +9617,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
   </conditionalFormatting>
